--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53438314935844</v>
+        <v>2.361837261770746</v>
       </c>
       <c r="D2" t="n">
-        <v>17.77674063009864</v>
+        <v>2.88872035239103</v>
       </c>
       <c r="E2" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F2" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.41775432629973</v>
+        <v>4.130385078023706</v>
       </c>
       <c r="D3" t="n">
-        <v>23.06359263979008</v>
+        <v>3.747833803965889</v>
       </c>
       <c r="E3" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F3" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.38778430322058</v>
+        <v>6.563014949273344</v>
       </c>
       <c r="D4" t="n">
-        <v>36.67845406833791</v>
+        <v>5.960248786104911</v>
       </c>
       <c r="E4" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F4" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.2903089552921</v>
+        <v>2.322175205234966</v>
       </c>
       <c r="D5" t="n">
-        <v>14.0415557579197</v>
+        <v>2.281752810661951</v>
       </c>
       <c r="E5" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F5" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.16708069526825</v>
+        <v>10.26465061298109</v>
       </c>
       <c r="D6" t="n">
-        <v>62.65851679969324</v>
+        <v>10.18200897995015</v>
       </c>
       <c r="E6" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F6" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.11719487452414</v>
+        <v>7.494044167110173</v>
       </c>
       <c r="D7" t="n">
-        <v>45.54691132036427</v>
+        <v>7.401373089559193</v>
       </c>
       <c r="E7" t="n">
-        <v>17.69832703618329</v>
+        <v>2.875978143379784</v>
       </c>
       <c r="F7" t="n">
-        <v>17.02922191374305</v>
+        <v>2.767248560983245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
